--- a/Luban/Datas/Level.xlsx
+++ b/Luban/Datas/Level.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LeiTing\Luban\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7BFCCD-1B41-4462-8E00-74C552CA4DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B792E27C-1192-45F0-ACDC-E5514ED4B8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="18720" windowHeight="11650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Level" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>第 1 关</t>
-  </si>
-  <si>
-    <t>Assets/Art/Sprites/Backgrounds/background-01.png</t>
   </si>
   <si>
     <t>level_02</t>
@@ -156,6 +153,10 @@
   </si>
   <si>
     <t>Assets/Art/Sprites/Backgrounds/background-03.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Sprites/Backgrounds/background-02.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -476,13 +477,13 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4">
         <v>2.1</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -490,16 +491,19 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>2.1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -507,16 +511,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
+      <c r="E6" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F6">
         <v>2.1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -524,16 +531,19 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
+      <c r="E7" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F7">
         <v>2.1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -541,16 +551,19 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
+      <c r="E8" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F8">
         <v>2.1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -558,16 +571,19 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
+      <c r="E9" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F9">
         <v>2.1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -575,16 +591,19 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F10">
         <v>2.1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -592,16 +611,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
+      <c r="E11" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F11">
         <v>2.1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -609,16 +631,19 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
         <v>34</v>
       </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
+      <c r="E12" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F12">
         <v>2.1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -626,16 +651,19 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
+      <c r="E13" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F13">
         <v>2.1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -643,16 +671,19 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
         <v>38</v>
       </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>19</v>
+      <c r="E14" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F14">
         <v>2.1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -660,16 +691,19 @@
         <v>12</v>
       </c>
       <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
         <v>40</v>
       </c>
-      <c r="D15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
+      <c r="E15" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F15">
         <v>2.1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
